--- a/public/exam_questions_sample.xlsx
+++ b/public/exam_questions_sample.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:R5"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -415,263 +415,295 @@
     <col min="14" max="14" width="25.83203125" customWidth="1"/>
     <col min="15" max="15" width="25.83203125" customWidth="1"/>
     <col min="16" max="16" width="25.83203125" customWidth="1"/>
+    <col min="17" max="17" width="25.83203125" customWidth="1"/>
+    <col min="18" max="18" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>Question ID</v>
+      </c>
+      <c r="B1" t="str">
         <v>Category Code (VOCAB, GRAMMAR, READING, LISTENING)</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>Mondai Title</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Passage</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Sentence Structure</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Prompt</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Choice 1</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Choice 2</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Choice 3</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Choice 4</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Correct Choice (1, 2, 3, or 4)</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Transcript</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Furigana</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>Translation (MM)</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Translation (EN)</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>Explanation (MM)</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>Explanation (EN)</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Audio Filename</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>N5-VOCAB-001</v>
+      </c>
+      <c r="B2" t="str">
         <v>VOCAB</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <v>もんだい１</v>
       </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
       <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>わたしは___です。</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>がくせい</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>せんせい</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>いしゃ</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>かいしゃいん</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>1</v>
       </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
       <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>わたしは___です。</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>ကျွန်တော်က ကျောင်းသားပါ။</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>I am a student.</v>
       </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
       <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>N5-GRAMMAR-001</v>
+      </c>
+      <c r="B3" t="str">
         <v>GRAMMAR</v>
       </c>
-      <c r="B3" t="str">
+      <c r="C3" t="str">
         <v>もんだい２</v>
       </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
       <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
         <v>Noun + です</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>これ___ほんです。</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>は</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>が</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>を</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>に</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>1</v>
       </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
       <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>これ___ほんです。</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>ဒါက စာအုပ်ဖြစ်ပါတယ်။</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>This is a book.</v>
       </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
       <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>N5-READING-001</v>
+      </c>
+      <c r="B4" t="str">
         <v>READING</v>
       </c>
-      <c r="B4" t="str">
+      <c r="C4" t="str">
         <v>もんだい３</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D4" t="str">
         <v>あしたはあめです。</v>
       </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>あしたのてんきは？</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>あめ</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>はれ</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>くもり</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>ゆき</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>1</v>
       </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
       <c r="L4" t="str">
         <v/>
       </c>
       <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
         <v>မနက်ဖြန် မိုးရွာမည်။</v>
       </c>
-      <c r="N4" t="str">
+      <c r="O4" t="str">
         <v>It will rain tomorrow.</v>
       </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
       <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
         <v/>
       </c>
     </row>
     <row r="5" xml:space="preserve">
       <c r="A5" t="str">
+        <v>N5-LISTENING-001</v>
+      </c>
+      <c r="B5" t="str">
         <v>LISTENING</v>
       </c>
-      <c r="B5" t="str">
+      <c r="C5" t="str">
         <v>もんだい４</v>
       </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
       <c r="D5" t="str">
         <v/>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>（Audio playing）男の人と女の人が話しています...</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
         <v>A</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>B</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>C</v>
       </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
         <v>D</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>1</v>
       </c>
-      <c r="K5" t="str" xml:space="preserve">
+      <c r="L5" t="str" xml:space="preserve">
         <v xml:space="preserve">男：こんにちは。
 女：こんにちは。</v>
       </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
       <c r="M5" t="str">
         <v/>
       </c>
-      <c r="N5" t="str" xml:space="preserve">
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str" xml:space="preserve">
         <v xml:space="preserve">Man: Hello.
 Woman: Hello.</v>
       </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
       <c r="P5" t="str">
         <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v>audio1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R5"/>
   </ignoredErrors>
 </worksheet>
 </file>